--- a/output/MASTER_DATASET.xlsx
+++ b/output/MASTER_DATASET.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="MASTER_MATCH" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="MASTER_DATASET" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E293"/>
+  <dimension ref="A1:J293"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -424,22 +424,47 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Категория</t>
+          <t>CATEGORY</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Бренд</t>
+          <t>BRAND</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Аромат</t>
+          <t>VARIANT</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Объем</t>
+          <t>VOLUME</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>AROMA</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>C7</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>C8</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>C9</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>MASTER_NAME</t>
         </is>
       </c>
     </row>
@@ -469,6 +494,19 @@
           <t>400 мл</t>
         </is>
       </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Cherry</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Гель для душа GILAR Cherry 400 мл</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -496,6 +534,19 @@
           <t>400 мл</t>
         </is>
       </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Avocado</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Гель для душа GILAR Avocado 400 мл</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -523,6 +574,19 @@
           <t>400 мл</t>
         </is>
       </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Гель для душа GILAR Mango 400 мл</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -550,6 +614,19 @@
           <t>400 мл</t>
         </is>
       </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Blackberry</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Гель для душа GILAR Blackberry 400 мл</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -577,6 +654,19 @@
           <t>400 мл</t>
         </is>
       </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Intense</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Шампунь women GILAR Intense 400 мл</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -604,6 +694,19 @@
           <t>400 мл</t>
         </is>
       </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Charm</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Шампунь women GILAR Charm 400 мл</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -631,6 +734,19 @@
           <t>400 мл</t>
         </is>
       </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Lovely Moments</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Шампунь women GILAR Lovely Moments 400 мл</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -658,6 +774,19 @@
           <t>400 мл</t>
         </is>
       </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Argan Oil</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Шампунь men GILAR Argan Oil 400 мл</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -685,6 +814,19 @@
           <t>400 мл</t>
         </is>
       </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Keratin Extracts</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Шампунь men GILAR Keratin Extracts 400 мл</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -712,6 +854,19 @@
           <t>400 мл</t>
         </is>
       </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Lemon Oil</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Шампунь men GILAR Lemon Oil 400 мл</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -739,6 +894,19 @@
           <t>400 мл</t>
         </is>
       </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Olive Oil</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Шампунь men GILAR Olive Oil 400 мл</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -766,6 +934,19 @@
           <t>400 мл</t>
         </is>
       </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Шампунь sport GILAR Black 400 мл</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -793,6 +974,19 @@
           <t>400 мл</t>
         </is>
       </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Blue</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Шампунь sport GILAR Blue 400 мл</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -820,6 +1014,19 @@
           <t>600 мл</t>
         </is>
       </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Almond</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Шампунь GILAR Almond 600 мл</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -847,6 +1054,19 @@
           <t>600 мл</t>
         </is>
       </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Aloe Vera</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Шампунь GILAR Aloe Vera 600 мл</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -874,6 +1094,19 @@
           <t>600 мл</t>
         </is>
       </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Garlic</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Шампунь GILAR Garlic 600 мл</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -901,6 +1134,19 @@
           <t>600 мл</t>
         </is>
       </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Keratin</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Шампунь GILAR Keratin 600 мл</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -928,6 +1174,19 @@
           <t>600 мл</t>
         </is>
       </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Mint</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Шампунь GILAR Mint 600 мл</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -955,6 +1214,19 @@
           <t>600 мл</t>
         </is>
       </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Nettle</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Шампунь GILAR Nettle 600 мл</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -982,6 +1254,19 @@
           <t>500 мл</t>
         </is>
       </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Argan Oil</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Шампунь органический GILAR Argan Oil 500 мл</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1009,6 +1294,19 @@
           <t>500 мл</t>
         </is>
       </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Coffee</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Шампунь органический GILAR Coffee 500 мл</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1036,6 +1334,19 @@
           <t>500 мл</t>
         </is>
       </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Ginger</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Шампунь органический GILAR Ginger 500 мл</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1063,6 +1374,19 @@
           <t>500 мл</t>
         </is>
       </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Lavender</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Шампунь органический GILAR Lavender 500 мл</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1090,6 +1414,19 @@
           <t>500 мл</t>
         </is>
       </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Ginseng</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Шампунь органический GILAR Ginseng 500 мл</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1117,6 +1454,19 @@
           <t>1 л</t>
         </is>
       </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Baby</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Baby 1 л</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1144,6 +1494,19 @@
           <t>1 л</t>
         </is>
       </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Midnight</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Midnight 1 л</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1171,6 +1534,19 @@
           <t>1 л</t>
         </is>
       </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Velvet</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Velvet 1 л</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1198,6 +1574,19 @@
           <t>1 л</t>
         </is>
       </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Floral Mist</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Floral Mist 1 л</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1225,6 +1614,19 @@
           <t>1 л</t>
         </is>
       </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Sweet Tropic</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Sweet Tropic 1 л</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1252,6 +1654,19 @@
           <t>1 л</t>
         </is>
       </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Dream</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Dream 1 л</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1279,6 +1694,19 @@
           <t>1 л</t>
         </is>
       </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Black 1 л</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1306,6 +1734,19 @@
           <t>1 л</t>
         </is>
       </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Saffran</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Saffran 1 л</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1333,6 +1774,19 @@
           <t>1,44 л</t>
         </is>
       </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Magina</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Magina 1,44 л</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1360,6 +1814,19 @@
           <t>1,44 л</t>
         </is>
       </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Velvet</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Velvet 1,44 л</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1387,6 +1854,19 @@
           <t>1,44 л</t>
         </is>
       </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Lotos</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Lotos 1,44 л</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1414,6 +1894,19 @@
           <t>1,44 л</t>
         </is>
       </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Mango 1,44 л</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1441,6 +1934,19 @@
           <t>1,44 л</t>
         </is>
       </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Dream</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Dream 1,44 л</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1468,6 +1974,19 @@
           <t>1,44 л</t>
         </is>
       </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Midnight</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Midnight 1,44 л</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1495,6 +2014,19 @@
           <t>1,44 л</t>
         </is>
       </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Tutkulu Dahlia</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Tutkulu Dahlia 1,44 л</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1522,6 +2054,19 @@
           <t>1,44 л</t>
         </is>
       </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Papatya</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Papatya 1,44 л</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1549,6 +2094,19 @@
           <t>1,44 л</t>
         </is>
       </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Floral Mist</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Floral Mist 1,44 л</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1576,6 +2134,19 @@
           <t>1,44 л</t>
         </is>
       </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Passion Fruit</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Passion Fruit 1,44 л</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1603,6 +2174,19 @@
           <t>1,44 л</t>
         </is>
       </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Orchide</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Orchide 1,44 л</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1630,6 +2214,19 @@
           <t>1,44 л</t>
         </is>
       </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Saffran</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Saffran 1,44 л</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1657,6 +2254,19 @@
           <t>1,44 л</t>
         </is>
       </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Shaik</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Shaik 1,44 л</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1684,6 +2294,19 @@
           <t>1,44 л</t>
         </is>
       </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Jasmin</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Jasmin 1,44 л</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1711,6 +2334,19 @@
           <t>1,44 л</t>
         </is>
       </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Romantik Rose</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Romantik Rose 1,44 л</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1738,6 +2374,19 @@
           <t>1,44 л</t>
         </is>
       </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Sweet Tropic</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Sweet Tropic 1,44 л</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1765,6 +2414,19 @@
           <t>1,44 л</t>
         </is>
       </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Rose</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Rose 1,44 л</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1792,6 +2454,19 @@
           <t>1,44 л</t>
         </is>
       </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Botanic September Sun</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Botanic September Sun 1,44 л</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1819,6 +2494,19 @@
           <t>1,44 л</t>
         </is>
       </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Botanic Rainy April</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Botanic Rainy April 1,44 л</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1846,6 +2534,19 @@
           <t>1,44 л</t>
         </is>
       </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Blackberry</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Blackberry 1,44 л</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1873,6 +2574,19 @@
           <t>1,44 л</t>
         </is>
       </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Baby</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Baby 1,44 л</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1900,6 +2614,19 @@
           <t>1,44 л</t>
         </is>
       </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>UD Premium</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO UD Premium 1,44 л</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1927,6 +2654,19 @@
           <t>2,7 л</t>
         </is>
       </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Peony</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Peony 2,7 л</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1954,6 +2694,19 @@
           <t>2,7 л</t>
         </is>
       </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Mountain Breeze</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Mountain Breeze 2,7 л</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1981,6 +2734,19 @@
           <t>2,7 л</t>
         </is>
       </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Black 2,7 л</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2008,6 +2774,19 @@
           <t>2,7 л</t>
         </is>
       </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Vanilla</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Vanilla 2,7 л</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2035,6 +2814,19 @@
           <t>2,7 л</t>
         </is>
       </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Lavender</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Lavender 2,7 л</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2062,6 +2854,19 @@
           <t>2,7 л</t>
         </is>
       </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Rose</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Rose 2,7 л</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2089,6 +2894,19 @@
           <t>2,7 л</t>
         </is>
       </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Papatya</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Papatya 2,7 л</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2116,6 +2934,19 @@
           <t>2,7 л</t>
         </is>
       </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Midnight</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Midnight 2,7 л</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2143,6 +2974,19 @@
           <t>2,7 л</t>
         </is>
       </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Dahlia</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Dahlia 2,7 л</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2170,6 +3014,19 @@
           <t>2,7 л</t>
         </is>
       </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Lotos</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Lotos 2,7 л</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2197,6 +3054,19 @@
           <t>2,7 л</t>
         </is>
       </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Floral Mist</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Floral Mist 2,7 л</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2224,6 +3094,19 @@
           <t>2,7 л</t>
         </is>
       </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Mango 2,7 л</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2251,6 +3134,19 @@
           <t>2,7 л</t>
         </is>
       </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Black Gel</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Black Gel 2,7 л</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2278,6 +3174,19 @@
           <t>5 л</t>
         </is>
       </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Ask 5 л</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2305,6 +3214,19 @@
           <t>5 л</t>
         </is>
       </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Frezya</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Frezya 5 л</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2332,6 +3254,19 @@
           <t>5 л</t>
         </is>
       </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Gul</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Gul 5 л</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2359,6 +3294,19 @@
           <t>5 л</t>
         </is>
       </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Huzur</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Huzur 5 л</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2386,6 +3334,19 @@
           <t>5 л</t>
         </is>
       </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Maiden Tower</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Maiden Tower 5 л</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2413,6 +3374,19 @@
           <t>5 л</t>
         </is>
       </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Love Is</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Кондиционер SVO Love Is 5 л</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2440,6 +3414,19 @@
           <t>1 л</t>
         </is>
       </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>White</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>ЖМС SVO Elegant White 1 л</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2467,6 +3454,19 @@
           <t>1 л</t>
         </is>
       </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Dream</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>ЖМС SVO Elegant Dream 1 л</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2494,6 +3494,19 @@
           <t>1 л</t>
         </is>
       </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Floral Mist</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>ЖМС SVO Elegant Floral Mist 1 л</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2521,6 +3534,19 @@
           <t>1 л</t>
         </is>
       </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Midnight</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>ЖМС SVO Elegant Midnight 1 л</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2548,6 +3574,19 @@
           <t>1 л</t>
         </is>
       </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Spring</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>ЖМС SVO Elegant Spring 1 л</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2575,6 +3614,19 @@
           <t>1 л</t>
         </is>
       </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Sweet Tropic</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>ЖМС SVO Elegant Sweet Tropic 1 л</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2602,6 +3654,19 @@
           <t>1 л</t>
         </is>
       </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Velvet</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>ЖМС SVO Elegant Velvet 1 л</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2629,6 +3694,19 @@
           <t>1 л</t>
         </is>
       </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>ЖМС SVO Elegant Black 1 л</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2656,6 +3734,19 @@
           <t>1 л</t>
         </is>
       </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Baby</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>ЖМС BOSSFIX Baby 1 л</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2683,6 +3774,19 @@
           <t>1,5 л</t>
         </is>
       </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>White</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>ЖМС SVO Elegant White 1,5 л</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2710,6 +3814,19 @@
           <t>1,5 л</t>
         </is>
       </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>ЖМС SVO Elegant Mango 1,5 л</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2737,6 +3854,19 @@
           <t>1,5 л</t>
         </is>
       </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Floral Mist</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>ЖМС SVO Elegant Floral Mist 1,5 л</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2764,6 +3894,19 @@
           <t>1,5 л</t>
         </is>
       </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Midnight</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>ЖМС SVO Elegant Midnight 1,5 л</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -2791,6 +3934,19 @@
           <t>1,5 л</t>
         </is>
       </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Spring</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>ЖМС SVO Elegant Spring 1,5 л</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -2818,6 +3974,19 @@
           <t>1,5 л</t>
         </is>
       </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Sweet Tropic</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>ЖМС SVO Elegant Sweet Tropic 1,5 л</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -2845,6 +4014,19 @@
           <t>1,5 л</t>
         </is>
       </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Velvet</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>ЖМС SVO Elegant Velvet 1,5 л</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -2872,6 +4054,19 @@
           <t>1,5 л</t>
         </is>
       </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Dream</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>ЖМС SVO Elegant Dream 1,5 л</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -2899,6 +4094,19 @@
           <t>1,5 л</t>
         </is>
       </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>ЖМС SVO Elegant Black 1,5 л</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -2926,6 +4134,19 @@
           <t>1,5 л</t>
         </is>
       </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Baby</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>ЖМС BOSSFIX Baby 1,5 л</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -2953,6 +4174,19 @@
           <t>1,5 л</t>
         </is>
       </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Baby</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>ЖМС SVO Baby 1,5 л</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -2980,6 +4214,19 @@
           <t>3 л</t>
         </is>
       </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Midnight</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>ЖМС SVO Midnight 3 л</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3007,6 +4254,19 @@
           <t>3 л</t>
         </is>
       </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Dream</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>ЖМС SVO Dream 3 л</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3034,6 +4294,19 @@
           <t>3 л</t>
         </is>
       </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Velvet</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>ЖМС SVO Velvet 3 л</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3061,6 +4334,19 @@
           <t>3 л</t>
         </is>
       </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Anti-Stain</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>ЖМС SVO Anti-Stain 3 л</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3088,6 +4374,19 @@
           <t>3 л</t>
         </is>
       </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>ЖМС SVO Black 3 л</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3115,6 +4414,19 @@
           <t>3 л</t>
         </is>
       </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Color</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>ЖМС SVO Color 3 л</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3142,6 +4454,19 @@
           <t>3 л</t>
         </is>
       </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>White</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>ЖМС SVO White 3 л</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3169,6 +4494,19 @@
           <t>3 л</t>
         </is>
       </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Mountain Breeze</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr"/>
+      <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>ЖМС SVO Mountain Breeze 3 л</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3196,6 +4534,19 @@
           <t>3 л</t>
         </is>
       </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Spring Fresh</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr"/>
+      <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>ЖМС SVO Spring Fresh 3 л</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3223,6 +4574,19 @@
           <t>3 л</t>
         </is>
       </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Baby</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr"/>
+      <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>ЖМС BOSSFIX Baby 3 л</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3250,6 +4614,19 @@
           <t>2,7 л</t>
         </is>
       </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Tutkulu Dahlia</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr"/>
+      <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>ЖМС 3в1 SVO Tutkulu Dahlia 2,7 л</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3277,6 +4654,19 @@
           <t>2,7 л</t>
         </is>
       </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Lavanda</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr"/>
+      <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>ЖМС 3в1 SVO Lavanda 2,7 л</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3304,6 +4694,19 @@
           <t>2,7 л</t>
         </is>
       </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Romantik Gul</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>ЖМС 3в1 SVO Romantik Gul 2,7 л</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3331,6 +4734,19 @@
           <t>2,7 л</t>
         </is>
       </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Floral Mist</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr"/>
+      <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>ЖМС 3в1 SVO Floral Mist 2,7 л</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3358,6 +4774,19 @@
           <t>2,7 л</t>
         </is>
       </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr"/>
+      <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>ЖМС 3в1 SVO Black 2,7 л</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -3385,6 +4814,19 @@
           <t>2,7 л</t>
         </is>
       </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Midnight</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr"/>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>ЖМС 3в1 SVO Midnight 2,7 л</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -3412,6 +4854,19 @@
           <t>500 мл</t>
         </is>
       </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Lavanda</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr"/>
+      <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>Жидкое мыло SVO Lavanda 500 мл</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -3439,6 +4894,19 @@
           <t>500 мл</t>
         </is>
       </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Ocean</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr"/>
+      <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>Жидкое мыло SVO Ocean 500 мл</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -3466,6 +4934,19 @@
           <t>500 мл</t>
         </is>
       </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Rose</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr"/>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>Жидкое мыло SVO Rose 500 мл</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -3493,6 +4974,19 @@
           <t>500 мл</t>
         </is>
       </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Olive</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr"/>
+      <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>Жидкое мыло SVO Olive 500 мл</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -3520,6 +5014,19 @@
           <t>500 мл</t>
         </is>
       </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Passion Fruit</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr"/>
+      <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>Жидкое мыло SVO Passion Fruit 500 мл</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -3547,6 +5054,19 @@
           <t>500 мл</t>
         </is>
       </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Chocolate</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr"/>
+      <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>Жидкое мыло SVO Chocolate 500 мл</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -3574,6 +5094,19 @@
           <t>500 мл</t>
         </is>
       </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr"/>
+      <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>Жидкое мыло SVO Mango 500 мл</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -3601,6 +5134,19 @@
           <t>500 мл</t>
         </is>
       </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Wild Berries</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr"/>
+      <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>Жидкое мыло SVO Wild Berries 500 мл</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -3628,6 +5174,19 @@
           <t>500 мл</t>
         </is>
       </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Coconut</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr"/>
+      <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>Крем-мыло GILAR Coconut 500 мл</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -3655,6 +5214,19 @@
           <t>500 мл</t>
         </is>
       </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Oatmeal</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr"/>
+      <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>Крем-мыло GILAR Oatmeal 500 мл</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -3682,6 +5254,19 @@
           <t>500 мл</t>
         </is>
       </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Oriental</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr"/>
+      <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>Крем-мыло GILAR Oriental 500 мл</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -3709,6 +5294,19 @@
           <t>500 мл</t>
         </is>
       </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Pine Forest</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr"/>
+      <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>Крем-мыло GILAR Pine Forest 500 мл</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -3736,6 +5334,19 @@
           <t>500 мл</t>
         </is>
       </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Cherry</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr"/>
+      <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>Крем-мыло GILAR Cherry 500 мл</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -3763,6 +5374,19 @@
           <t>500 мл</t>
         </is>
       </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Aloe Vera</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr"/>
+      <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>Натуральное мыло GILAR Aloe Vera 500 мл</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -3790,6 +5414,19 @@
           <t>500 мл</t>
         </is>
       </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Ginseng</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr"/>
+      <c r="H125" t="inlineStr"/>
+      <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>Натуральное мыло GILAR Ginseng 500 мл</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -3817,6 +5454,19 @@
           <t>500 мл</t>
         </is>
       </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Argan Oil</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr"/>
+      <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>Натуральное мыло GILAR Argan Oil 500 мл</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -3844,6 +5494,19 @@
           <t>500 мл</t>
         </is>
       </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Ginger</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr"/>
+      <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>Натуральное мыло GILAR Ginger 500 мл</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -3871,6 +5534,19 @@
           <t>500 мл</t>
         </is>
       </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Almond</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr"/>
+      <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>Натуральное мыло GILAR Almond 500 мл</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -3898,6 +5574,19 @@
           <t>500 мл</t>
         </is>
       </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Nut</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr"/>
+      <c r="H129" t="inlineStr"/>
+      <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>Натуральное мыло GILAR Nut 500 мл</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -3925,6 +5614,19 @@
           <t>500 мл</t>
         </is>
       </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Cotton Milk</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr"/>
+      <c r="H130" t="inlineStr"/>
+      <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>Натуральное мыло GILAR Cotton Milk 500 мл</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -3952,6 +5654,19 @@
           <t>500 мл</t>
         </is>
       </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Cactus Flower</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr"/>
+      <c r="H131" t="inlineStr"/>
+      <c r="I131" t="inlineStr"/>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>Натуральное мыло GILAR Cactus Flower 500 мл</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -3979,6 +5694,19 @@
           <t>500 мл</t>
         </is>
       </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Chocolate</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr"/>
+      <c r="H132" t="inlineStr"/>
+      <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>Натуральное мыло GILAR Chocolate 500 мл</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -4006,6 +5734,19 @@
           <t>4×85 г</t>
         </is>
       </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Grapefruit</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr"/>
+      <c r="H133" t="inlineStr"/>
+      <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>Сухое мыло Pearlis Grapefruit 4×85 г</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -4033,6 +5774,19 @@
           <t>4×85 г</t>
         </is>
       </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Bouquet</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr"/>
+      <c r="H134" t="inlineStr"/>
+      <c r="I134" t="inlineStr"/>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>Сухое мыло Pearlis Bouquet 4×85 г</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -4060,6 +5814,19 @@
           <t>4×85 г</t>
         </is>
       </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Green Tea</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr"/>
+      <c r="H135" t="inlineStr"/>
+      <c r="I135" t="inlineStr"/>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>Сухое мыло Pearlis Green Tea 4×85 г</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -4087,6 +5854,19 @@
           <t>4×85 г</t>
         </is>
       </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Sea Minerals</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr"/>
+      <c r="H136" t="inlineStr"/>
+      <c r="I136" t="inlineStr"/>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>Сухое мыло Pearlis Sea Minerals 4×85 г</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -4114,6 +5894,19 @@
           <t>4×100 г</t>
         </is>
       </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Bouquet</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr"/>
+      <c r="H137" t="inlineStr"/>
+      <c r="I137" t="inlineStr"/>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>Сухое мыло Pearlis Bouquet 4×100 г</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -4141,6 +5934,19 @@
           <t>4×100 г</t>
         </is>
       </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Sea Minerals</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr"/>
+      <c r="H138" t="inlineStr"/>
+      <c r="I138" t="inlineStr"/>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>Сухое мыло Pearlis Sea Minerals 4×100 г</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -4168,6 +5974,19 @@
           <t>4×100 г</t>
         </is>
       </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Rose</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr"/>
+      <c r="H139" t="inlineStr"/>
+      <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>Сухое мыло Pearlis Rose 4×100 г</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -4195,6 +6014,19 @@
           <t>1 л</t>
         </is>
       </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Pink</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr"/>
+      <c r="H140" t="inlineStr"/>
+      <c r="I140" t="inlineStr"/>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>Пол моющее средство SVO Pink 1 л</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -4222,6 +6054,19 @@
           <t>2,5 л</t>
         </is>
       </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Pink</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr"/>
+      <c r="H141" t="inlineStr"/>
+      <c r="I141" t="inlineStr"/>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>Пол моющее средство SVO Pink 2,5 л</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -4249,6 +6094,19 @@
           <t>1 л</t>
         </is>
       </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Purple</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr"/>
+      <c r="H142" t="inlineStr"/>
+      <c r="I142" t="inlineStr"/>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>Пол моющее средство SVO Purple 1 л</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -4276,6 +6134,19 @@
           <t>2,5 л</t>
         </is>
       </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Purple</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr"/>
+      <c r="H143" t="inlineStr"/>
+      <c r="I143" t="inlineStr"/>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>Пол моющее средство SVO Purple 2,5 л</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -4303,6 +6174,19 @@
           <t>750 г</t>
         </is>
       </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>White</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr"/>
+      <c r="H144" t="inlineStr"/>
+      <c r="I144" t="inlineStr"/>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>Отбеливатель SVO White 750 г</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -4330,6 +6214,19 @@
           <t>750 г</t>
         </is>
       </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Color</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr"/>
+      <c r="H145" t="inlineStr"/>
+      <c r="I145" t="inlineStr"/>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>Отбеливатель SVO Color 750 г</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -4357,6 +6254,19 @@
           <t>90 шт</t>
         </is>
       </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Baby</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr"/>
+      <c r="H146" t="inlineStr"/>
+      <c r="I146" t="inlineStr"/>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>Салфетки влажные BOSSFIX Baby 90 шт</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -4374,9 +6284,19 @@
           <t>Yunis Effendi</t>
         </is>
       </c>
+      <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr">
         <is>
           <t>100 г</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr"/>
+      <c r="G147" t="inlineStr"/>
+      <c r="H147" t="inlineStr"/>
+      <c r="I147" t="inlineStr"/>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>Кофе молотый Yunis Effendi  100 г</t>
         </is>
       </c>
     </row>
@@ -4396,9 +6316,19 @@
           <t>Yunis Effendi</t>
         </is>
       </c>
+      <c r="D148" t="inlineStr"/>
       <c r="E148" t="inlineStr">
         <is>
           <t>250 г</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr"/>
+      <c r="G148" t="inlineStr"/>
+      <c r="H148" t="inlineStr"/>
+      <c r="I148" t="inlineStr"/>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>Кофе молотый Yunis Effendi  250 г</t>
         </is>
       </c>
     </row>
@@ -4418,9 +6348,19 @@
           <t>Yunis Effendi</t>
         </is>
       </c>
+      <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr">
         <is>
           <t>500 г</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr"/>
+      <c r="G149" t="inlineStr"/>
+      <c r="H149" t="inlineStr"/>
+      <c r="I149" t="inlineStr"/>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>Кофе зерно Yunis Effendi  500 г</t>
         </is>
       </c>
     </row>
@@ -4450,6 +6390,19 @@
           <t>400 г</t>
         </is>
       </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Rose</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr"/>
+      <c r="H150" t="inlineStr"/>
+      <c r="I150" t="inlineStr"/>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Rose 400 г</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -4477,6 +6430,19 @@
           <t>400 г</t>
         </is>
       </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Lemon</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr"/>
+      <c r="H151" t="inlineStr"/>
+      <c r="I151" t="inlineStr"/>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Lemon 400 г</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -4504,6 +6470,19 @@
           <t>400 г</t>
         </is>
       </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Lavender</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr"/>
+      <c r="H152" t="inlineStr"/>
+      <c r="I152" t="inlineStr"/>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Lavender 400 г</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -4531,6 +6510,19 @@
           <t>400 г</t>
         </is>
       </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Mountain Breeze</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr"/>
+      <c r="H153" t="inlineStr"/>
+      <c r="I153" t="inlineStr"/>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Mountain Breeze 400 г</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -4558,6 +6550,19 @@
           <t>400 г</t>
         </is>
       </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Papatye</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr"/>
+      <c r="H154" t="inlineStr"/>
+      <c r="I154" t="inlineStr"/>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Papatye 400 г</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -4585,6 +6590,19 @@
           <t>400 г</t>
         </is>
       </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr"/>
+      <c r="H155" t="inlineStr"/>
+      <c r="I155" t="inlineStr"/>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Mango 400 г</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -4612,6 +6630,19 @@
           <t>400 г</t>
         </is>
       </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Passion Fruit</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr"/>
+      <c r="H156" t="inlineStr"/>
+      <c r="I156" t="inlineStr"/>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Passion Fruit 400 г</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -4639,6 +6670,19 @@
           <t>400 г</t>
         </is>
       </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr"/>
+      <c r="H157" t="inlineStr"/>
+      <c r="I157" t="inlineStr"/>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Black 400 г</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -4666,6 +6710,19 @@
           <t>400 г</t>
         </is>
       </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Color</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr"/>
+      <c r="H158" t="inlineStr"/>
+      <c r="I158" t="inlineStr"/>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Color 400 г</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -4693,6 +6750,19 @@
           <t>400 г</t>
         </is>
       </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Snowdrop</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr"/>
+      <c r="H159" t="inlineStr"/>
+      <c r="I159" t="inlineStr"/>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Snowdrop 400 г</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -4720,6 +6790,19 @@
           <t>400 г</t>
         </is>
       </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Spring Fresh</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr"/>
+      <c r="H160" t="inlineStr"/>
+      <c r="I160" t="inlineStr"/>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Spring Fresh 400 г</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -4747,6 +6830,19 @@
           <t>1,3 кг</t>
         </is>
       </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Rose</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr"/>
+      <c r="H161" t="inlineStr"/>
+      <c r="I161" t="inlineStr"/>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Rose 1,3 кг</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -4774,6 +6870,19 @@
           <t>1,3 кг</t>
         </is>
       </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Lemon</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr"/>
+      <c r="H162" t="inlineStr"/>
+      <c r="I162" t="inlineStr"/>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Lemon 1,3 кг</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -4801,6 +6910,19 @@
           <t>1,3 кг</t>
         </is>
       </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Lavender</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr"/>
+      <c r="H163" t="inlineStr"/>
+      <c r="I163" t="inlineStr"/>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Lavender 1,3 кг</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -4828,6 +6950,19 @@
           <t>1,3 кг</t>
         </is>
       </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Mountain Breeze</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr"/>
+      <c r="H164" t="inlineStr"/>
+      <c r="I164" t="inlineStr"/>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Mountain Breeze 1,3 кг</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -4855,6 +6990,19 @@
           <t>1,3 кг</t>
         </is>
       </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>Papatye</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr"/>
+      <c r="H165" t="inlineStr"/>
+      <c r="I165" t="inlineStr"/>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Papatye 1,3 кг</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -4882,6 +7030,19 @@
           <t>1,3 кг</t>
         </is>
       </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr"/>
+      <c r="H166" t="inlineStr"/>
+      <c r="I166" t="inlineStr"/>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Mango 1,3 кг</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -4909,6 +7070,19 @@
           <t>1,3 кг</t>
         </is>
       </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Passion Fruit</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr"/>
+      <c r="H167" t="inlineStr"/>
+      <c r="I167" t="inlineStr"/>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Passion Fruit 1,3 кг</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -4936,6 +7110,19 @@
           <t>1,3 кг</t>
         </is>
       </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr"/>
+      <c r="H168" t="inlineStr"/>
+      <c r="I168" t="inlineStr"/>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Black 1,3 кг</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -4963,6 +7150,19 @@
           <t>1,3 кг</t>
         </is>
       </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Color</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr"/>
+      <c r="H169" t="inlineStr"/>
+      <c r="I169" t="inlineStr"/>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Color 1,3 кг</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -4990,6 +7190,19 @@
           <t>1,3 кг</t>
         </is>
       </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Snowdrop</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr"/>
+      <c r="H170" t="inlineStr"/>
+      <c r="I170" t="inlineStr"/>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Snowdrop 1,3 кг</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -5017,6 +7230,19 @@
           <t>1,3 кг</t>
         </is>
       </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>Spring Fresh</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr"/>
+      <c r="H171" t="inlineStr"/>
+      <c r="I171" t="inlineStr"/>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Spring Fresh 1,3 кг</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -5044,6 +7270,19 @@
           <t>1,3 кг</t>
         </is>
       </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>Baby</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr"/>
+      <c r="H172" t="inlineStr"/>
+      <c r="I172" t="inlineStr"/>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Baby 1,3 кг</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -5071,6 +7310,19 @@
           <t>1,5 кг</t>
         </is>
       </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>Rose</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr"/>
+      <c r="H173" t="inlineStr"/>
+      <c r="I173" t="inlineStr"/>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Rose 1,5 кг</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -5098,6 +7350,19 @@
           <t>1,5 кг</t>
         </is>
       </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>Lemon</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr"/>
+      <c r="H174" t="inlineStr"/>
+      <c r="I174" t="inlineStr"/>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Lemon 1,5 кг</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -5125,6 +7390,19 @@
           <t>1,5 кг</t>
         </is>
       </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>Lavender</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr"/>
+      <c r="H175" t="inlineStr"/>
+      <c r="I175" t="inlineStr"/>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Lavender 1,5 кг</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -5152,6 +7430,19 @@
           <t>1,5 кг</t>
         </is>
       </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>Mountain Breeze</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr"/>
+      <c r="H176" t="inlineStr"/>
+      <c r="I176" t="inlineStr"/>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Mountain Breeze 1,5 кг</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -5179,6 +7470,19 @@
           <t>1,5 кг</t>
         </is>
       </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>Papatye</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr"/>
+      <c r="H177" t="inlineStr"/>
+      <c r="I177" t="inlineStr"/>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Papatye 1,5 кг</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -5206,6 +7510,19 @@
           <t>1,5 кг</t>
         </is>
       </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr"/>
+      <c r="H178" t="inlineStr"/>
+      <c r="I178" t="inlineStr"/>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Mango 1,5 кг</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -5233,6 +7550,19 @@
           <t>1,5 кг</t>
         </is>
       </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>Passion Fruit</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr"/>
+      <c r="H179" t="inlineStr"/>
+      <c r="I179" t="inlineStr"/>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Passion Fruit 1,5 кг</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -5260,6 +7590,19 @@
           <t>1,5 кг</t>
         </is>
       </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr"/>
+      <c r="H180" t="inlineStr"/>
+      <c r="I180" t="inlineStr"/>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Black 1,5 кг</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -5287,6 +7630,19 @@
           <t>1,5 кг</t>
         </is>
       </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>Color</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr"/>
+      <c r="H181" t="inlineStr"/>
+      <c r="I181" t="inlineStr"/>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Color 1,5 кг</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -5314,6 +7670,19 @@
           <t>1,5 кг</t>
         </is>
       </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>Snowdrop</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr"/>
+      <c r="H182" t="inlineStr"/>
+      <c r="I182" t="inlineStr"/>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Snowdrop 1,5 кг</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -5341,6 +7710,19 @@
           <t>1,5 кг</t>
         </is>
       </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>Spring Fresh</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr"/>
+      <c r="H183" t="inlineStr"/>
+      <c r="I183" t="inlineStr"/>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Spring Fresh 1,5 кг</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -5368,6 +7750,19 @@
           <t>2,7 кг</t>
         </is>
       </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>Rose</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr"/>
+      <c r="H184" t="inlineStr"/>
+      <c r="I184" t="inlineStr"/>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Rose 2,7 кг</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -5395,6 +7790,19 @@
           <t>2,7 кг</t>
         </is>
       </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>Lemon</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr"/>
+      <c r="H185" t="inlineStr"/>
+      <c r="I185" t="inlineStr"/>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Lemon 2,7 кг</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -5422,6 +7830,19 @@
           <t>2,7 кг</t>
         </is>
       </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Lavender</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr"/>
+      <c r="H186" t="inlineStr"/>
+      <c r="I186" t="inlineStr"/>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Lavender 2,7 кг</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -5449,6 +7870,19 @@
           <t>2,7 кг</t>
         </is>
       </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Mountain Breeze</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr"/>
+      <c r="H187" t="inlineStr"/>
+      <c r="I187" t="inlineStr"/>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Mountain Breeze 2,7 кг</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -5476,6 +7910,19 @@
           <t>2,7 кг</t>
         </is>
       </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>Papatye</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr"/>
+      <c r="H188" t="inlineStr"/>
+      <c r="I188" t="inlineStr"/>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Papatye 2,7 кг</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -5503,6 +7950,19 @@
           <t>2,7 кг</t>
         </is>
       </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr"/>
+      <c r="H189" t="inlineStr"/>
+      <c r="I189" t="inlineStr"/>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Mango 2,7 кг</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -5530,6 +7990,19 @@
           <t>2,7 кг</t>
         </is>
       </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Passion Fruit</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr"/>
+      <c r="H190" t="inlineStr"/>
+      <c r="I190" t="inlineStr"/>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Passion Fruit 2,7 кг</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -5557,6 +8030,19 @@
           <t>2,7 кг</t>
         </is>
       </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr"/>
+      <c r="H191" t="inlineStr"/>
+      <c r="I191" t="inlineStr"/>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Black 2,7 кг</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -5584,6 +8070,19 @@
           <t>2,7 кг</t>
         </is>
       </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>Color</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr"/>
+      <c r="H192" t="inlineStr"/>
+      <c r="I192" t="inlineStr"/>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Color 2,7 кг</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -5611,6 +8110,19 @@
           <t>2,7 кг</t>
         </is>
       </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>Snowdrop</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr"/>
+      <c r="H193" t="inlineStr"/>
+      <c r="I193" t="inlineStr"/>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Snowdrop 2,7 кг</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -5638,6 +8150,19 @@
           <t>2,7 кг</t>
         </is>
       </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>Spring Fresh</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr"/>
+      <c r="H194" t="inlineStr"/>
+      <c r="I194" t="inlineStr"/>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Spring Fresh 2,7 кг</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -5665,6 +8190,19 @@
           <t>3 кг</t>
         </is>
       </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>Rose</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr"/>
+      <c r="H195" t="inlineStr"/>
+      <c r="I195" t="inlineStr"/>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Rose 3 кг</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -5692,6 +8230,19 @@
           <t>3 кг</t>
         </is>
       </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>Lemon</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr"/>
+      <c r="H196" t="inlineStr"/>
+      <c r="I196" t="inlineStr"/>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Lemon 3 кг</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -5719,6 +8270,19 @@
           <t>3 кг</t>
         </is>
       </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>Lavender</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr"/>
+      <c r="H197" t="inlineStr"/>
+      <c r="I197" t="inlineStr"/>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Lavender 3 кг</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -5746,6 +8310,19 @@
           <t>3 кг</t>
         </is>
       </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>Mountain Breeze</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr"/>
+      <c r="H198" t="inlineStr"/>
+      <c r="I198" t="inlineStr"/>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Mountain Breeze 3 кг</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -5773,6 +8350,19 @@
           <t>3 кг</t>
         </is>
       </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>Papatye</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr"/>
+      <c r="H199" t="inlineStr"/>
+      <c r="I199" t="inlineStr"/>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Papatye 3 кг</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -5800,6 +8390,19 @@
           <t>3 кг</t>
         </is>
       </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr"/>
+      <c r="H200" t="inlineStr"/>
+      <c r="I200" t="inlineStr"/>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Mango 3 кг</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -5827,6 +8430,19 @@
           <t>3 кг</t>
         </is>
       </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>Passion Fruit</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr"/>
+      <c r="H201" t="inlineStr"/>
+      <c r="I201" t="inlineStr"/>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Passion Fruit 3 кг</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -5854,6 +8470,19 @@
           <t>3 кг</t>
         </is>
       </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr"/>
+      <c r="H202" t="inlineStr"/>
+      <c r="I202" t="inlineStr"/>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Black 3 кг</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -5881,6 +8510,19 @@
           <t>3 кг</t>
         </is>
       </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>Color</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr"/>
+      <c r="H203" t="inlineStr"/>
+      <c r="I203" t="inlineStr"/>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Color 3 кг</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -5908,6 +8550,19 @@
           <t>3 кг</t>
         </is>
       </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>Snowdrop</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr"/>
+      <c r="H204" t="inlineStr"/>
+      <c r="I204" t="inlineStr"/>
+      <c r="J204" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Snowdrop 3 кг</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -5935,6 +8590,19 @@
           <t>3 кг</t>
         </is>
       </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>Spring Fresh</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr"/>
+      <c r="H205" t="inlineStr"/>
+      <c r="I205" t="inlineStr"/>
+      <c r="J205" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Spring Fresh 3 кг</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -5962,6 +8630,19 @@
           <t>4 кг</t>
         </is>
       </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>Rose</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr"/>
+      <c r="H206" t="inlineStr"/>
+      <c r="I206" t="inlineStr"/>
+      <c r="J206" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Rose 4 кг</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -5989,6 +8670,19 @@
           <t>4 кг</t>
         </is>
       </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>Lemon</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr"/>
+      <c r="H207" t="inlineStr"/>
+      <c r="I207" t="inlineStr"/>
+      <c r="J207" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Lemon 4 кг</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -6016,6 +8710,19 @@
           <t>4 кг</t>
         </is>
       </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>Lavender</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr"/>
+      <c r="H208" t="inlineStr"/>
+      <c r="I208" t="inlineStr"/>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Lavender 4 кг</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -6043,6 +8750,19 @@
           <t>4 кг</t>
         </is>
       </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>Mountain Breeze</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr"/>
+      <c r="H209" t="inlineStr"/>
+      <c r="I209" t="inlineStr"/>
+      <c r="J209" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Mountain Breeze 4 кг</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -6070,6 +8790,19 @@
           <t>4 кг</t>
         </is>
       </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>Papatye</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr"/>
+      <c r="H210" t="inlineStr"/>
+      <c r="I210" t="inlineStr"/>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Papatye 4 кг</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -6097,6 +8830,19 @@
           <t>4 кг</t>
         </is>
       </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr"/>
+      <c r="H211" t="inlineStr"/>
+      <c r="I211" t="inlineStr"/>
+      <c r="J211" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Mango 4 кг</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -6124,6 +8870,19 @@
           <t>4 кг</t>
         </is>
       </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>Passion Fruit</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr"/>
+      <c r="H212" t="inlineStr"/>
+      <c r="I212" t="inlineStr"/>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Passion Fruit 4 кг</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -6151,6 +8910,19 @@
           <t>4 кг</t>
         </is>
       </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr"/>
+      <c r="H213" t="inlineStr"/>
+      <c r="I213" t="inlineStr"/>
+      <c r="J213" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Black 4 кг</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -6178,6 +8950,19 @@
           <t>4 кг</t>
         </is>
       </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>Color</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr"/>
+      <c r="H214" t="inlineStr"/>
+      <c r="I214" t="inlineStr"/>
+      <c r="J214" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Color 4 кг</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -6205,6 +8990,19 @@
           <t>4 кг</t>
         </is>
       </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>Snowdrop</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr"/>
+      <c r="H215" t="inlineStr"/>
+      <c r="I215" t="inlineStr"/>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Snowdrop 4 кг</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -6232,11 +9030,24 @@
           <t>4 кг</t>
         </is>
       </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>Spring Fresh</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr"/>
+      <c r="H216" t="inlineStr"/>
+      <c r="I216" t="inlineStr"/>
+      <c r="J216" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Spring Fresh 4 кг</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t xml:space="preserve">SKU-295 </t>
+          <t>SKU-295</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -6257,6 +9068,19 @@
       <c r="E217" t="inlineStr">
         <is>
           <t>5 кг</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>Magina</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr"/>
+      <c r="H217" t="inlineStr"/>
+      <c r="I217" t="inlineStr"/>
+      <c r="J217" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Magina 5 кг</t>
         </is>
       </c>
     </row>
@@ -6286,6 +9110,19 @@
           <t>6 кг</t>
         </is>
       </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>Rose</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr"/>
+      <c r="H218" t="inlineStr"/>
+      <c r="I218" t="inlineStr"/>
+      <c r="J218" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Rose 6 кг</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -6313,6 +9150,19 @@
           <t>6 кг</t>
         </is>
       </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>Lemon</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr"/>
+      <c r="H219" t="inlineStr"/>
+      <c r="I219" t="inlineStr"/>
+      <c r="J219" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Lemon 6 кг</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -6340,6 +9190,19 @@
           <t>6 кг</t>
         </is>
       </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>Lavender</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr"/>
+      <c r="H220" t="inlineStr"/>
+      <c r="I220" t="inlineStr"/>
+      <c r="J220" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Lavender 6 кг</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -6367,6 +9230,19 @@
           <t>6 кг</t>
         </is>
       </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>Mountain Breeze</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr"/>
+      <c r="H221" t="inlineStr"/>
+      <c r="I221" t="inlineStr"/>
+      <c r="J221" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Mountain Breeze 6 кг</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -6394,6 +9270,19 @@
           <t>6 кг</t>
         </is>
       </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>Papatye</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr"/>
+      <c r="H222" t="inlineStr"/>
+      <c r="I222" t="inlineStr"/>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Papatye 6 кг</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -6421,6 +9310,19 @@
           <t>6 кг</t>
         </is>
       </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr"/>
+      <c r="H223" t="inlineStr"/>
+      <c r="I223" t="inlineStr"/>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Mango 6 кг</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -6448,6 +9350,19 @@
           <t>6 кг</t>
         </is>
       </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>Passion Fruit</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr"/>
+      <c r="H224" t="inlineStr"/>
+      <c r="I224" t="inlineStr"/>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Passion Fruit 6 кг</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -6475,6 +9390,19 @@
           <t>6 кг</t>
         </is>
       </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr"/>
+      <c r="H225" t="inlineStr"/>
+      <c r="I225" t="inlineStr"/>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Black 6 кг</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -6502,6 +9430,19 @@
           <t>6 кг</t>
         </is>
       </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>Color</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr"/>
+      <c r="H226" t="inlineStr"/>
+      <c r="I226" t="inlineStr"/>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Color 6 кг</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -6529,6 +9470,19 @@
           <t>6 кг</t>
         </is>
       </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>Snowdrop</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr"/>
+      <c r="H227" t="inlineStr"/>
+      <c r="I227" t="inlineStr"/>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Snowdrop 6 кг</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -6556,6 +9510,19 @@
           <t>6 кг</t>
         </is>
       </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>Spring Fresh</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr"/>
+      <c r="H228" t="inlineStr"/>
+      <c r="I228" t="inlineStr"/>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Spring Fresh 6 кг</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -6583,6 +9550,19 @@
           <t>9 кг</t>
         </is>
       </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>Rose</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr"/>
+      <c r="H229" t="inlineStr"/>
+      <c r="I229" t="inlineStr"/>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Rose 9 кг</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -6610,6 +9590,19 @@
           <t>9 кг</t>
         </is>
       </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>Lemon</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr"/>
+      <c r="H230" t="inlineStr"/>
+      <c r="I230" t="inlineStr"/>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Lemon 9 кг</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -6637,6 +9630,19 @@
           <t>9 кг</t>
         </is>
       </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>Lavender</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr"/>
+      <c r="H231" t="inlineStr"/>
+      <c r="I231" t="inlineStr"/>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Lavender 9 кг</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -6664,6 +9670,19 @@
           <t>9 кг</t>
         </is>
       </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>Mountain Breeze</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr"/>
+      <c r="H232" t="inlineStr"/>
+      <c r="I232" t="inlineStr"/>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Mountain Breeze 9 кг</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -6691,6 +9710,19 @@
           <t>9 кг</t>
         </is>
       </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>Papatye</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr"/>
+      <c r="H233" t="inlineStr"/>
+      <c r="I233" t="inlineStr"/>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Papatye 9 кг</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -6718,6 +9750,19 @@
           <t>9 кг</t>
         </is>
       </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr"/>
+      <c r="H234" t="inlineStr"/>
+      <c r="I234" t="inlineStr"/>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Mango 9 кг</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -6745,6 +9790,19 @@
           <t>9 кг</t>
         </is>
       </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>Passion Fruit</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr"/>
+      <c r="H235" t="inlineStr"/>
+      <c r="I235" t="inlineStr"/>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Passion Fruit 9 кг</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -6772,6 +9830,19 @@
           <t>9 кг</t>
         </is>
       </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr"/>
+      <c r="H236" t="inlineStr"/>
+      <c r="I236" t="inlineStr"/>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Black 9 кг</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -6799,6 +9870,19 @@
           <t>9 кг</t>
         </is>
       </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>Color</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr"/>
+      <c r="H237" t="inlineStr"/>
+      <c r="I237" t="inlineStr"/>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Color 9 кг</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -6826,6 +9910,19 @@
           <t>9 кг</t>
         </is>
       </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>Snowdrop</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr"/>
+      <c r="H238" t="inlineStr"/>
+      <c r="I238" t="inlineStr"/>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Snowdrop 9 кг</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -6853,6 +9950,19 @@
           <t>9 кг</t>
         </is>
       </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>Spring Fresh</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr"/>
+      <c r="H239" t="inlineStr"/>
+      <c r="I239" t="inlineStr"/>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Spring Fresh 9 кг</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -6880,6 +9990,19 @@
           <t>10 кг</t>
         </is>
       </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>Rose</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr"/>
+      <c r="H240" t="inlineStr"/>
+      <c r="I240" t="inlineStr"/>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Rose 10 кг</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -6907,6 +10030,19 @@
           <t>10 кг</t>
         </is>
       </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>Lemon</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr"/>
+      <c r="H241" t="inlineStr"/>
+      <c r="I241" t="inlineStr"/>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Lemon 10 кг</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -6934,6 +10070,19 @@
           <t>10 кг</t>
         </is>
       </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>Lavender</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr"/>
+      <c r="H242" t="inlineStr"/>
+      <c r="I242" t="inlineStr"/>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Lavender 10 кг</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -6961,6 +10110,19 @@
           <t>10 кг</t>
         </is>
       </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>Mountain Breeze</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr"/>
+      <c r="H243" t="inlineStr"/>
+      <c r="I243" t="inlineStr"/>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Mountain Breeze 10 кг</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -6988,6 +10150,19 @@
           <t>10 кг</t>
         </is>
       </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>Papatye</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr"/>
+      <c r="H244" t="inlineStr"/>
+      <c r="I244" t="inlineStr"/>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Papatye 10 кг</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -7015,6 +10190,19 @@
           <t>10 кг</t>
         </is>
       </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr"/>
+      <c r="H245" t="inlineStr"/>
+      <c r="I245" t="inlineStr"/>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Mango 10 кг</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -7042,6 +10230,19 @@
           <t>10 кг</t>
         </is>
       </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>Passion Fruit</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr"/>
+      <c r="H246" t="inlineStr"/>
+      <c r="I246" t="inlineStr"/>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Passion Fruit 10 кг</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -7069,6 +10270,19 @@
           <t>10 кг</t>
         </is>
       </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>Black</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr"/>
+      <c r="H247" t="inlineStr"/>
+      <c r="I247" t="inlineStr"/>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Black 10 кг</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -7096,6 +10310,19 @@
           <t>10 кг</t>
         </is>
       </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>Color</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr"/>
+      <c r="H248" t="inlineStr"/>
+      <c r="I248" t="inlineStr"/>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Color 10 кг</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -7123,6 +10350,19 @@
           <t>10 кг</t>
         </is>
       </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>Snowdrop</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr"/>
+      <c r="H249" t="inlineStr"/>
+      <c r="I249" t="inlineStr"/>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Snowdrop 10 кг</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -7150,6 +10390,19 @@
           <t>10 кг</t>
         </is>
       </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>Spring Fresh</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr"/>
+      <c r="H250" t="inlineStr"/>
+      <c r="I250" t="inlineStr"/>
+      <c r="J250" t="inlineStr">
+        <is>
+          <t>Порошок стиральный SVO Spring Fresh 10 кг</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -7177,6 +10430,19 @@
           <t>2×48 г</t>
         </is>
       </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>Lemon</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr"/>
+      <c r="H251" t="inlineStr"/>
+      <c r="I251" t="inlineStr"/>
+      <c r="J251" t="inlineStr">
+        <is>
+          <t>Блок туалетный SVO Lemon 2×48 г</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -7204,6 +10470,19 @@
           <t>48 г</t>
         </is>
       </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>Lemon</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr"/>
+      <c r="H252" t="inlineStr"/>
+      <c r="I252" t="inlineStr"/>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>Блок туалетный SVO Lemon 48 г</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -7231,6 +10510,19 @@
           <t>2×48 г</t>
         </is>
       </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>Ocean</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr"/>
+      <c r="H253" t="inlineStr"/>
+      <c r="I253" t="inlineStr"/>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t>Блок туалетный SVO Ocean 2×48 г</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -7258,6 +10550,19 @@
           <t>48 г</t>
         </is>
       </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>Ocean</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr"/>
+      <c r="H254" t="inlineStr"/>
+      <c r="I254" t="inlineStr"/>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>Блок туалетный SVO Ocean 48 г</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -7285,6 +10590,19 @@
           <t>2×48 г</t>
         </is>
       </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>Pine</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr"/>
+      <c r="H255" t="inlineStr"/>
+      <c r="I255" t="inlineStr"/>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>Блок туалетный SVO Pine 2×48 г</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -7312,6 +10630,19 @@
           <t>48 г</t>
         </is>
       </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>Pine</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr"/>
+      <c r="H256" t="inlineStr"/>
+      <c r="I256" t="inlineStr"/>
+      <c r="J256" t="inlineStr">
+        <is>
+          <t>Блок туалетный SVO Pine 48 г</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -7339,6 +10670,19 @@
           <t>2×48 г</t>
         </is>
       </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>Flowers</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr"/>
+      <c r="H257" t="inlineStr"/>
+      <c r="I257" t="inlineStr"/>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>Блок туалетный SVO Flowers 2×48 г</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -7366,6 +10710,19 @@
           <t>48 г</t>
         </is>
       </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>Flowers</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr"/>
+      <c r="H258" t="inlineStr"/>
+      <c r="I258" t="inlineStr"/>
+      <c r="J258" t="inlineStr">
+        <is>
+          <t>Блок туалетный SVO Flowers 48 г</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -7393,6 +10750,19 @@
           <t>750 мл</t>
         </is>
       </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>Orange</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr"/>
+      <c r="H259" t="inlineStr"/>
+      <c r="I259" t="inlineStr"/>
+      <c r="J259" t="inlineStr">
+        <is>
+          <t>Посуда моющее ср-во SVO Orange 750 мл</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -7420,6 +10790,19 @@
           <t>750 мл</t>
         </is>
       </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>Grapefruit</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr"/>
+      <c r="H260" t="inlineStr"/>
+      <c r="I260" t="inlineStr"/>
+      <c r="J260" t="inlineStr">
+        <is>
+          <t>Посуда моющее ср-во SVO Grapefruit 750 мл</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -7447,6 +10830,19 @@
           <t>750 мл</t>
         </is>
       </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>Lemon</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr"/>
+      <c r="H261" t="inlineStr"/>
+      <c r="I261" t="inlineStr"/>
+      <c r="J261" t="inlineStr">
+        <is>
+          <t>Посуда моющее ср-во SVO Lemon 750 мл</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -7474,6 +10870,19 @@
           <t>750 мл</t>
         </is>
       </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr"/>
+      <c r="H262" t="inlineStr"/>
+      <c r="I262" t="inlineStr"/>
+      <c r="J262" t="inlineStr">
+        <is>
+          <t>Посуда моющее ср-во SVO Apple 750 мл</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -7501,6 +10910,19 @@
           <t>750 мл</t>
         </is>
       </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr"/>
+      <c r="H263" t="inlineStr"/>
+      <c r="I263" t="inlineStr"/>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>Посуда моющее ср-во SVO Mango 750 мл</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -7528,6 +10950,19 @@
           <t>1 л</t>
         </is>
       </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>Orange</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr"/>
+      <c r="H264" t="inlineStr"/>
+      <c r="I264" t="inlineStr"/>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>Посуда моющее ср-во SVO Orange 1 л</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -7555,6 +10990,19 @@
           <t>1 л</t>
         </is>
       </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr"/>
+      <c r="H265" t="inlineStr"/>
+      <c r="I265" t="inlineStr"/>
+      <c r="J265" t="inlineStr">
+        <is>
+          <t>Посуда моющее ср-во SVO Pomegranate 1 л</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -7582,6 +11030,19 @@
           <t>1 л</t>
         </is>
       </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>Wild Berries</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr"/>
+      <c r="H266" t="inlineStr"/>
+      <c r="I266" t="inlineStr"/>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>Посуда моющее ср-во SVO Wild Berries 1 л</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -7609,6 +11070,19 @@
           <t>1 л</t>
         </is>
       </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>Ginger</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr"/>
+      <c r="H267" t="inlineStr"/>
+      <c r="I267" t="inlineStr"/>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>Посуда моющее ср-во SVO Ginger 1 л</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -7636,6 +11110,19 @@
           <t>1 л</t>
         </is>
       </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>Strawberry</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr"/>
+      <c r="H268" t="inlineStr"/>
+      <c r="I268" t="inlineStr"/>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t>Посуда моющее ср-во SVO Strawberry 1 л</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -7663,6 +11150,19 @@
           <t>1 л</t>
         </is>
       </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>Lemon</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr"/>
+      <c r="H269" t="inlineStr"/>
+      <c r="I269" t="inlineStr"/>
+      <c r="J269" t="inlineStr">
+        <is>
+          <t>Посуда моющее ср-во SVO Lemon 1 л</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -7690,6 +11190,19 @@
           <t>1 л</t>
         </is>
       </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr"/>
+      <c r="H270" t="inlineStr"/>
+      <c r="I270" t="inlineStr"/>
+      <c r="J270" t="inlineStr">
+        <is>
+          <t>Посуда моющее ср-во SVO Mango 1 л</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -7717,6 +11230,19 @@
           <t>1 л</t>
         </is>
       </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>Passion</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr"/>
+      <c r="H271" t="inlineStr"/>
+      <c r="I271" t="inlineStr"/>
+      <c r="J271" t="inlineStr">
+        <is>
+          <t>Посуда моющее ср-во SVO Passion 1 л</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -7744,6 +11270,19 @@
           <t>1 л</t>
         </is>
       </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr"/>
+      <c r="H272" t="inlineStr"/>
+      <c r="I272" t="inlineStr"/>
+      <c r="J272" t="inlineStr">
+        <is>
+          <t>Посуда моющее ср-во SVO Apple 1 л</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -7771,6 +11310,19 @@
           <t>2 л</t>
         </is>
       </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>Orange</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr"/>
+      <c r="H273" t="inlineStr"/>
+      <c r="I273" t="inlineStr"/>
+      <c r="J273" t="inlineStr">
+        <is>
+          <t>Посуда моющее ср-во SVO Orange 2 л</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -7798,6 +11350,19 @@
           <t>2 л</t>
         </is>
       </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>Lemon</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr"/>
+      <c r="H274" t="inlineStr"/>
+      <c r="I274" t="inlineStr"/>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>Посуда моющее ср-во SVO Lemon 2 л</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -7825,6 +11390,19 @@
           <t>2 л</t>
         </is>
       </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>Wild Berries</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr"/>
+      <c r="H275" t="inlineStr"/>
+      <c r="I275" t="inlineStr"/>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t>Посуда моющее ср-во SVO Wild Berries 2 л</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -7852,6 +11430,19 @@
           <t>2 л</t>
         </is>
       </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr"/>
+      <c r="H276" t="inlineStr"/>
+      <c r="I276" t="inlineStr"/>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>Посуда моющее ср-во SVO Apple 2 л</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -7879,6 +11470,19 @@
           <t>2 л</t>
         </is>
       </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>Ginger</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr"/>
+      <c r="H277" t="inlineStr"/>
+      <c r="I277" t="inlineStr"/>
+      <c r="J277" t="inlineStr">
+        <is>
+          <t>Посуда моющее ср-во SVO Ginger 2 л</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -7906,6 +11510,19 @@
           <t>2 л</t>
         </is>
       </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>Passion Fruit</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr"/>
+      <c r="H278" t="inlineStr"/>
+      <c r="I278" t="inlineStr"/>
+      <c r="J278" t="inlineStr">
+        <is>
+          <t>Посуда моющее ср-во SVO Passion Fruit 2 л</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -7933,6 +11550,19 @@
           <t>2 л</t>
         </is>
       </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>Pomegranate</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr"/>
+      <c r="H279" t="inlineStr"/>
+      <c r="I279" t="inlineStr"/>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>Посуда моющее ср-во SVO Pomegranate 2 л</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -7960,6 +11590,19 @@
           <t>2 л</t>
         </is>
       </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>Strawberry</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr"/>
+      <c r="H280" t="inlineStr"/>
+      <c r="I280" t="inlineStr"/>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>Посуда моющее ср-во SVO Strawberry 2 л</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -7987,6 +11630,19 @@
           <t>2 л</t>
         </is>
       </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>Mango</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr"/>
+      <c r="H281" t="inlineStr"/>
+      <c r="I281" t="inlineStr"/>
+      <c r="J281" t="inlineStr">
+        <is>
+          <t>Посуда моющее ср-во SVO Mango 2 л</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -8014,6 +11670,19 @@
           <t>4 л</t>
         </is>
       </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>Orange</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr"/>
+      <c r="H282" t="inlineStr"/>
+      <c r="I282" t="inlineStr"/>
+      <c r="J282" t="inlineStr">
+        <is>
+          <t>Посуда моющее ср-во SVO Orange 4 л</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -8041,6 +11710,19 @@
           <t>4 л</t>
         </is>
       </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>Grapefruit</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr"/>
+      <c r="H283" t="inlineStr"/>
+      <c r="I283" t="inlineStr"/>
+      <c r="J283" t="inlineStr">
+        <is>
+          <t>Посуда моющее ср-во SVO Grapefruit 4 л</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -8068,6 +11750,19 @@
           <t>4 л</t>
         </is>
       </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>Lemon</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr"/>
+      <c r="H284" t="inlineStr"/>
+      <c r="I284" t="inlineStr"/>
+      <c r="J284" t="inlineStr">
+        <is>
+          <t>Посуда моющее ср-во SVO Lemon 4 л</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -8095,48 +11790,74 @@
           <t>4 л</t>
         </is>
       </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr"/>
+      <c r="H285" t="inlineStr"/>
+      <c r="I285" t="inlineStr"/>
+      <c r="J285" t="inlineStr">
+        <is>
+          <t>Посуда моющее ср-во SVO Apple 4 л</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t xml:space="preserve">SKU-283 </t>
+          <t>SKU-283</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t xml:space="preserve">Подгузники </t>
+          <t>Подгузники</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t xml:space="preserve">BOSSFIX </t>
+          <t>BOSSFIX</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t xml:space="preserve">Size 1 </t>
+          <t>Size 1</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
           <t>1 уп</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>Size 1</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr"/>
+      <c r="H286" t="inlineStr"/>
+      <c r="I286" t="inlineStr"/>
+      <c r="J286" t="inlineStr">
+        <is>
+          <t>Подгузники BOSSFIX Size 1 1 уп</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t xml:space="preserve">SKU-284 </t>
+          <t>SKU-284</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t xml:space="preserve">Подгузники </t>
+          <t>Подгузники</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t xml:space="preserve">BOSSFIX </t>
+          <t>BOSSFIX</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -8147,23 +11868,36 @@
       <c r="E287" t="inlineStr">
         <is>
           <t>1 уп</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>Size 2</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr"/>
+      <c r="H287" t="inlineStr"/>
+      <c r="I287" t="inlineStr"/>
+      <c r="J287" t="inlineStr">
+        <is>
+          <t>Подгузники BOSSFIX Size 2 1 уп</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t xml:space="preserve">SKU-285 </t>
+          <t>SKU-285</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t xml:space="preserve">Подгузники </t>
+          <t>Подгузники</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t xml:space="preserve">BOSSFIX </t>
+          <t>BOSSFIX</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -8174,23 +11908,36 @@
       <c r="E288" t="inlineStr">
         <is>
           <t>1 уп</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>Size 3</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr"/>
+      <c r="H288" t="inlineStr"/>
+      <c r="I288" t="inlineStr"/>
+      <c r="J288" t="inlineStr">
+        <is>
+          <t>Подгузники BOSSFIX Size 3 1 уп</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t xml:space="preserve">SKU-286 </t>
+          <t>SKU-286</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t xml:space="preserve">Подгузники </t>
+          <t>Подгузники</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t xml:space="preserve">BOSSFIX </t>
+          <t>BOSSFIX</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -8201,23 +11948,36 @@
       <c r="E289" t="inlineStr">
         <is>
           <t>1 уп</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>Size 4</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr"/>
+      <c r="H289" t="inlineStr"/>
+      <c r="I289" t="inlineStr"/>
+      <c r="J289" t="inlineStr">
+        <is>
+          <t>Подгузники BOSSFIX Size 4 1 уп</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t xml:space="preserve">SKU-287 </t>
+          <t>SKU-287</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t xml:space="preserve">Подгузники </t>
+          <t>Подгузники</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t xml:space="preserve">BOSSFIX </t>
+          <t>BOSSFIX</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -8228,23 +11988,36 @@
       <c r="E290" t="inlineStr">
         <is>
           <t>1 уп</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>Size 5</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr"/>
+      <c r="H290" t="inlineStr"/>
+      <c r="I290" t="inlineStr"/>
+      <c r="J290" t="inlineStr">
+        <is>
+          <t>Подгузники BOSSFIX Size 5 1 уп</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t xml:space="preserve">SKU-288 </t>
+          <t>SKU-288</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t xml:space="preserve">Подгузники </t>
+          <t>Подгузники</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t xml:space="preserve">BOSSFIX </t>
+          <t>BOSSFIX</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -8255,13 +12028,26 @@
       <c r="E291" t="inlineStr">
         <is>
           <t>1 уп</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>Size 6</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr"/>
+      <c r="H291" t="inlineStr"/>
+      <c r="I291" t="inlineStr"/>
+      <c r="J291" t="inlineStr">
+        <is>
+          <t>Подгузники BOSSFIX Size 6 1 уп</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t xml:space="preserve">SKU-289 </t>
+          <t>SKU-289</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -8274,16 +12060,26 @@
           <t>DOMIX</t>
         </is>
       </c>
+      <c r="D292" t="inlineStr"/>
       <c r="E292" t="inlineStr">
         <is>
           <t>1 л</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr"/>
+      <c r="G292" t="inlineStr"/>
+      <c r="H292" t="inlineStr"/>
+      <c r="I292" t="inlineStr"/>
+      <c r="J292" t="inlineStr">
+        <is>
+          <t>Антинакипь DOMIX  1 л</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t xml:space="preserve">SKU-290 </t>
+          <t>SKU-290</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -8296,9 +12092,19 @@
           <t>DOMIX</t>
         </is>
       </c>
+      <c r="D293" t="inlineStr"/>
       <c r="E293" t="inlineStr">
         <is>
           <t>1 л</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr"/>
+      <c r="G293" t="inlineStr"/>
+      <c r="H293" t="inlineStr"/>
+      <c r="I293" t="inlineStr"/>
+      <c r="J293" t="inlineStr">
+        <is>
+          <t>Антижир DOMIX  1 л</t>
         </is>
       </c>
     </row>
